--- a/מילון נתונים ומאגרים/מילון נתונים.xlsx
+++ b/מילון נתונים ומאגרים/מילון נתונים.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leong\Desktop\Pet\second year\ניתוח מערכות מידע\מילון נתונים ומאגרים\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9A00CC-28B2-46CB-B961-0238A969E9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB767ACF-8F07-4B32-992A-ABF9B48298FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6A504C6D-3976-49FF-A78B-47E345B0F30A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6A504C6D-3976-49FF-A78B-47E345B0F30A}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="149">
   <si>
     <t>קוד</t>
   </si>
@@ -455,10 +455,6 @@
 Message_id </t>
   </si>
   <si>
-    <t xml:space="preserve">Receiver_ID, content, Sender_ID,  Is_accsept  
-</t>
-  </si>
-  <si>
     <t>user_name1,user_name2
 friendship_status</t>
   </si>
@@ -490,6 +486,22 @@
   </si>
   <si>
     <t xml:space="preserve">category_events </t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>רשימת ערים</t>
+  </si>
+  <si>
+    <t>cities</t>
+  </si>
+  <si>
+    <t>List_cities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receiver_ID, content, Sender_ID,  type 
+</t>
   </si>
 </sst>
 </file>
@@ -646,12 +658,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -989,21 +1001,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2978B75B-C8C1-4DDB-895B-233F094AC0CA}">
   <dimension ref="B2:D74"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="40.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="40.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="C2" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
@@ -1014,7 +1026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1025,7 +1037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
@@ -1036,25 +1048,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="2:4" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:4" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:4" ht="24.6" x14ac:dyDescent="0.4">
       <c r="D11" s="1"/>
     </row>
-    <row r="21" spans="4:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:4" ht="15" x14ac:dyDescent="0.25">
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="4:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:4" ht="15" x14ac:dyDescent="0.25">
       <c r="D22" s="2"/>
     </row>
-    <row r="33" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="C33" s="8"/>
     </row>
-    <row r="35" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="C35" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
         <v>0</v>
       </c>
@@ -1065,7 +1077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:4" ht="54" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" ht="52.2" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>10</v>
       </c>
@@ -1076,7 +1088,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="2:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>11</v>
       </c>
@@ -1087,7 +1099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="54" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" ht="52.2" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>13</v>
       </c>
@@ -1098,7 +1110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>14</v>
       </c>
@@ -1109,7 +1121,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="2:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>15</v>
       </c>
@@ -1120,7 +1132,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>16</v>
       </c>
@@ -1131,7 +1143,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4" ht="70.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="6" t="s">
         <v>17</v>
       </c>
@@ -1142,20 +1154,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="D46" s="10"/>
     </row>
-    <row r="51" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="C52" s="11" t="s">
         <v>96</v>
       </c>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
         <v>0</v>
       </c>
@@ -1166,7 +1178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>33</v>
       </c>
@@ -1177,7 +1189,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>36</v>
       </c>
@@ -1188,7 +1200,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>39</v>
       </c>
@@ -1199,7 +1211,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="2:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
         <v>40</v>
       </c>
@@ -1210,7 +1222,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>45</v>
       </c>
@@ -1221,7 +1233,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>48</v>
       </c>
@@ -1232,7 +1244,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>51</v>
       </c>
@@ -1243,7 +1255,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>54</v>
       </c>
@@ -1254,7 +1266,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>57</v>
       </c>
@@ -1265,7 +1277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>60</v>
       </c>
@@ -1276,7 +1288,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>63</v>
       </c>
@@ -1287,7 +1299,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>94</v>
       </c>
@@ -1298,7 +1310,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B66" s="4" t="s">
         <v>66</v>
       </c>
@@ -1309,7 +1321,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B67" s="4" t="s">
         <v>69</v>
       </c>
@@ -1320,7 +1332,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B68" s="4" t="s">
         <v>72</v>
       </c>
@@ -1331,7 +1343,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>75</v>
       </c>
@@ -1342,7 +1354,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
         <v>78</v>
       </c>
@@ -1353,7 +1365,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
         <v>81</v>
       </c>
@@ -1364,7 +1376,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>84</v>
       </c>
@@ -1375,7 +1387,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>87</v>
       </c>
@@ -1386,7 +1398,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="74" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
         <v>89</v>
       </c>
@@ -1405,21 +1417,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0933AA19-EE63-4E3A-9898-EC955CD955FD}">
-  <dimension ref="A2:D15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:D16"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B2" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1445,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="72" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>101</v>
       </c>
@@ -1447,7 +1459,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>109</v>
       </c>
@@ -1458,10 +1470,10 @@
         <v>118</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>110</v>
       </c>
@@ -1475,7 +1487,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>111</v>
       </c>
@@ -1489,7 +1501,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>112</v>
       </c>
@@ -1503,7 +1515,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>113</v>
       </c>
@@ -1517,7 +1529,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>114</v>
       </c>
@@ -1528,10 +1540,10 @@
         <v>122</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>115</v>
       </c>
@@ -1542,10 +1554,10 @@
         <v>123</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>108</v>
       </c>
@@ -1559,32 +1571,46 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+    <row r="14" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="18" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>144</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
